--- a/inst/resources/tool_household_iphra_v2.xlsx
+++ b/inst/resources/tool_household_iphra_v2.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\Documents\GitHub\iphraApp\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7B3E0A-37B7-45E2-9921-9886B4F26F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49F56CE-7D8F-451C-8C60-F48FDEDCAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="h2fYSiQvhiNGkrtUsLkSn45g315KWDSA25bD4j3ORM5bRlKWMnBDtzvS6AbBSYAj6ag3ODyY1mEUTQPcGFJ0Tg==" workbookSaltValue="IfpCe47h0g637JARLrp1Sg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5312" uniqueCount="3409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="3410">
   <si>
     <t>indicator_code</t>
   </si>
@@ -10302,6 +10302,9 @@
   </si>
   <si>
     <t>ما هو نوع الناموسية؟</t>
+  </si>
+  <si>
+    <t>comment</t>
   </si>
 </sst>
 </file>
@@ -10612,21 +10615,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11630,7 +11633,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>1803</v>
@@ -11659,7 +11662,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>1809</v>
@@ -11688,7 +11691,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>1814</v>
@@ -11717,7 +11720,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>1819</v>
@@ -11746,7 +11749,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1824</v>
@@ -11804,7 +11807,7 @@
         <v>60</v>
       </c>
       <c r="B22" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C22" t="s">
         <v>1834</v>
@@ -11862,7 +11865,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C24" t="s">
         <v>1847</v>
@@ -11906,7 +11909,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C25" t="s">
         <v>1858</v>
@@ -11935,7 +11938,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C26" t="s">
         <v>1834</v>
@@ -11964,7 +11967,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C27" t="s">
         <v>1847</v>
@@ -11996,7 +11999,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C28" t="s">
         <v>1858</v>
@@ -12839,7 +12842,7 @@
         <v>30</v>
       </c>
       <c r="B61" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C61" t="s">
         <v>1923</v>
@@ -12869,7 +12872,7 @@
         <v>0</v>
       </c>
       <c r="B62" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C62" t="s">
         <v>1772</v>
@@ -12901,7 +12904,7 @@
         <v>30</v>
       </c>
       <c r="B63" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C63" t="s">
         <v>1923</v>
@@ -12934,7 +12937,7 @@
         <v>0</v>
       </c>
       <c r="B64" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C64" t="s">
         <v>1772</v>
@@ -12966,7 +12969,7 @@
         <v>30</v>
       </c>
       <c r="B65" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C65" t="s">
         <v>1923</v>
@@ -12999,7 +13002,7 @@
         <v>0</v>
       </c>
       <c r="B66" s="4">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="C66" t="s">
         <v>1772</v>
@@ -21655,11 +21658,14 @@
       <c r="A338" s="7">
         <v>5</v>
       </c>
-      <c r="B338">
-        <v>10000</v>
+      <c r="B338" s="4">
+        <v>10001</v>
       </c>
       <c r="C338" s="11" t="s">
         <v>1772</v>
+      </c>
+      <c r="D338" s="11" t="s">
+        <v>3409</v>
       </c>
       <c r="E338" s="13" t="s">
         <v>3346</v>
@@ -21720,14 +21726,14 @@
   <conditionalFormatting sqref="D110:D111 D118:D128 D132:D203 D233:D234 D238 D333">
     <cfRule type="duplicateValues" dxfId="14" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D258:D295 D129:D130 D1:D11 D16:D22 D210:D232 D241:D242 D298:D299 D302:D304 D308 D319:D328 D330:D332 D334:D1048576 D67:D101 D244:D249 D251:D253">
-    <cfRule type="duplicateValues" dxfId="13" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D239:D240">
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D254:D257">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D258:D295 D129:D130 D1:D11 D16:D22 D210:D232 D241:D242 D298:D299 D302:D304 D308 D319:D328 D330:D332 D334:D1048576 D67:D101 D244:D249 D251:D253">
+    <cfRule type="duplicateValues" dxfId="11" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D301">
     <cfRule type="duplicateValues" dxfId="10" priority="3"/>
@@ -32770,221 +32776,221 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="46" t="s">
         <v>3360</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>3361</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="42" t="s">
         <v>3362</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="47"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="44"/>
     </row>
     <row r="4" spans="2:14" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="33" t="s">
         <v>3363</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="45" t="s">
         <v>3364</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="47"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="44"/>
     </row>
     <row r="5" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
         <v>3365</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="42" t="s">
         <v>3366</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="47"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="44"/>
     </row>
     <row r="6" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="35" t="s">
         <v>3367</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="49" t="s">
         <v>3368</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="47"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="44"/>
     </row>
     <row r="7" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="42" t="s">
         <v>3370</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="47"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="44"/>
     </row>
     <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="42" t="s">
         <v>3371</v>
       </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="47"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="44"/>
     </row>
     <row r="9" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="42" t="s">
         <v>3372</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="47"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="44"/>
     </row>
     <row r="10" spans="2:14" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="42" t="s">
         <v>3373</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="47"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="44"/>
     </row>
     <row r="11" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="42" t="s">
         <v>3374</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="47"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="44"/>
     </row>
     <row r="12" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="42" t="s">
         <v>3375</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="47"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="44"/>
     </row>
     <row r="13" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="42" t="s">
         <v>3376</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="47"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="44"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="37"/>
@@ -32995,233 +33001,224 @@
       <c r="G14" s="38"/>
     </row>
     <row r="15" spans="2:14" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="46" t="s">
         <v>3360</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48"/>
     </row>
     <row r="16" spans="2:14" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="33" t="s">
         <v>3377</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="42" t="s">
         <v>3378</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="47"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="44"/>
     </row>
     <row r="17" spans="2:14" ht="71.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="33" t="s">
         <v>3363</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="45" t="s">
         <v>3379</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="47"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="44"/>
     </row>
     <row r="18" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
         <v>3380</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="42" t="s">
         <v>3381</v>
       </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="47"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="44"/>
     </row>
     <row r="19" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="35" t="s">
         <v>3382</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="49" t="s">
         <v>3383</v>
       </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="47"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="44"/>
     </row>
     <row r="20" spans="2:14" ht="53.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="42" t="s">
         <v>3384</v>
       </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="47"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="44"/>
     </row>
     <row r="21" spans="2:14" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="42" t="s">
         <v>3385</v>
       </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="47"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="44"/>
     </row>
     <row r="22" spans="2:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="42" t="s">
         <v>3386</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="47"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="44"/>
     </row>
     <row r="23" spans="2:14" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="42" t="s">
         <v>3387</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="47"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="44"/>
     </row>
     <row r="24" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="42" t="s">
         <v>3388</v>
       </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="47"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="44"/>
     </row>
     <row r="25" spans="2:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="42" t="s">
         <v>3389</v>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="47"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="44"/>
     </row>
     <row r="26" spans="2:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="36" t="s">
         <v>3369</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="42" t="s">
         <v>3390</v>
       </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="47"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C26:N26"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C20:N20"/>
-    <mergeCell ref="C25:N25"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="C22:N22"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="C11:N11"/>
-    <mergeCell ref="C23:N23"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="C6:N6"/>
@@ -33237,6 +33234,15 @@
     <mergeCell ref="C21:N21"/>
     <mergeCell ref="C10:N10"/>
     <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C26:N26"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="C25:N25"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="C22:N22"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="C11:N11"/>
+    <mergeCell ref="C23:N23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
